--- a/URIARTE 630/Agosto/EXPENSAS-Agosto.xlsx
+++ b/URIARTE 630/Agosto/EXPENSAS-Agosto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\URIARTE 630\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\URIARTE 630\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F900908F-7099-4656-95D8-6E9B35C05456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{331E429A-65A2-4AD7-802B-2849DB810399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -233,13 +233,13 @@
     <t>Ingreso pago de expensas en termino</t>
   </si>
   <si>
-    <t>ARTICULOS DE LIMPIEZA</t>
-  </si>
-  <si>
-    <t>Vto. 14/08</t>
-  </si>
-  <si>
-    <t>Liquidacion mes de JULIO</t>
+    <t>SERVISUR REGULACION DE SENSORES DE MOVIMIENTO</t>
+  </si>
+  <si>
+    <t>Vto. 15/09</t>
+  </si>
+  <si>
+    <t>Liquidacion mes de AGOSTO</t>
   </si>
 </sst>
 </file>
@@ -1176,6 +1176,29 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1191,12 +1214,6 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1206,23 +1223,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1671,15 +1671,14 @@
       </c>
       <c r="B12" s="48"/>
       <c r="C12" s="105">
-        <f>65200*5%+65200</f>
-        <v>68460</v>
+        <v>71833</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="31" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="32">
-        <v>-626184.19407167984</v>
+        <v>-606603.76407167991</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1688,7 +1687,7 @@
       </c>
       <c r="B13" s="48"/>
       <c r="C13" s="105">
-        <v>3567.21</v>
+        <v>4519.7749999999996</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="33" t="s">
@@ -1696,7 +1695,7 @@
       </c>
       <c r="F13" s="57">
         <f>'prorrateo '!F10</f>
-        <v>630015</v>
+        <v>484610.18209999998</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1704,16 +1703,14 @@
         <v>56</v>
       </c>
       <c r="B14" s="48"/>
-      <c r="C14" s="46">
-        <v>85014.2</v>
-      </c>
+      <c r="C14" s="46"/>
       <c r="D14" s="24"/>
       <c r="E14" s="33" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="77">
         <f>-C36 +C30</f>
-        <v>-610434.57000000007</v>
+        <v>-533469.41500000004</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1734,7 +1731,7 @@
       </c>
       <c r="B16" s="56"/>
       <c r="C16" s="105">
-        <v>42387.21</v>
+        <v>42359.76</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="33"/>
@@ -1758,7 +1755,7 @@
       </c>
       <c r="B18" s="55"/>
       <c r="C18" s="105">
-        <v>200413.74</v>
+        <v>211814.67</v>
       </c>
       <c r="E18" s="33"/>
       <c r="F18" s="34"/>
@@ -1768,9 +1765,7 @@
         <v>67</v>
       </c>
       <c r="B19" s="48"/>
-      <c r="C19" s="105">
-        <v>11630.8</v>
-      </c>
+      <c r="C19" s="105"/>
       <c r="E19" s="33"/>
       <c r="F19" s="34"/>
     </row>
@@ -1779,7 +1774,7 @@
       <c r="B20" s="50"/>
       <c r="C20" s="107">
         <f>SUM(C12:C18)</f>
-        <v>582784.57000000007</v>
+        <v>513469.41500000004</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="35" t="s">
@@ -1787,7 +1782,7 @@
       </c>
       <c r="F20" s="36">
         <f>SUM(F12:F18)</f>
-        <v>-606603.76407167991</v>
+        <v>-655462.99697167997</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1806,7 +1801,7 @@
       </c>
       <c r="B22" s="48"/>
       <c r="C22" s="46">
-        <v>27650</v>
+        <v>20000</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="12"/>
@@ -1817,7 +1812,7 @@
       <c r="B23" s="22"/>
       <c r="C23" s="47">
         <f>SUM(C21:C22)</f>
-        <v>27650</v>
+        <v>20000</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -1831,7 +1826,7 @@
       <c r="B24" s="27"/>
       <c r="C24" s="80">
         <f>+C23+C20</f>
-        <v>610434.57000000007</v>
+        <v>533469.41500000004</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="12"/>
@@ -1913,7 +1908,7 @@
       </c>
       <c r="C35" s="85">
         <f>C34+C24</f>
-        <v>610434.57000000007</v>
+        <v>533469.41500000004</v>
       </c>
       <c r="F35" s="5"/>
     </row>
@@ -1924,7 +1919,7 @@
       <c r="B36" s="40"/>
       <c r="C36" s="53">
         <f>+C24+C33</f>
-        <v>610434.57000000007</v>
+        <v>533469.41500000004</v>
       </c>
       <c r="E36" s="10"/>
     </row>
@@ -2025,33 +2020,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="120" t="str">
+      <c r="A1" s="129" t="str">
         <f>'detalle y gastos'!E7</f>
-        <v>Liquidacion mes de JULIO</v>
-      </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+        <v>Liquidacion mes de AGOSTO</v>
+      </c>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
       <c r="D1" s="91"/>
       <c r="E1" s="92" t="s">
         <v>35</v>
       </c>
       <c r="F1" s="91"/>
-      <c r="G1" s="111" t="s">
+      <c r="G1" s="124" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="114">
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+      <c r="J1" s="125"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="127">
         <v>610434.56999999995</v>
       </c>
-      <c r="M1" s="115"/>
+      <c r="M1" s="128"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="93" t="str">
         <f>'detalle y gastos'!F7</f>
-        <v>Vto. 14/08</v>
+        <v>Vto. 15/09</v>
       </c>
       <c r="B2" s="86"/>
       <c r="C2" s="86"/>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="L4" s="88" t="str">
         <f>A2</f>
-        <v>Vto. 14/08</v>
+        <v>Vto. 15/09</v>
       </c>
       <c r="M4" s="95" t="s">
         <v>65</v>
@@ -2161,19 +2156,18 @@
         <v>0.5</v>
       </c>
       <c r="E5" s="23">
-        <v>197172.75118799997</v>
+        <v>128164.01088799995</v>
       </c>
       <c r="F5" s="46">
-        <f>197200</f>
-        <v>197200</v>
+        <v>125000</v>
       </c>
       <c r="G5" s="89">
         <f>E5-F5</f>
-        <v>-27.248812000034377</v>
+        <v>3164.0108879999461</v>
       </c>
       <c r="H5" s="90">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>0</v>
+        <v>265.77691459199548</v>
       </c>
       <c r="I5" s="9">
         <v>0</v>
@@ -2188,11 +2182,11 @@
       </c>
       <c r="L5" s="9">
         <f>J5+K5+H5+G5</f>
-        <v>128164.01088799995</v>
+        <v>131621.04750259191</v>
       </c>
       <c r="M5" s="96">
         <f>L5+L5*4%</f>
-        <v>133290.57132351995</v>
+        <v>136885.88940269558</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2209,10 +2203,11 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="23">
-        <v>165218</v>
+        <v>101576</v>
       </c>
       <c r="F6" s="46">
-        <v>165218</v>
+        <f>E6</f>
+        <v>101576</v>
       </c>
       <c r="G6" s="89">
         <f t="shared" ref="G6:G9" si="0">E6-F6</f>
@@ -2254,18 +2249,16 @@
       </c>
       <c r="D7" s="52"/>
       <c r="E7" s="23">
-        <v>86882.394566129209</v>
-      </c>
-      <c r="F7" s="46">
-        <v>86882</v>
-      </c>
+        <v>128191.68740968405</v>
+      </c>
+      <c r="F7" s="46"/>
       <c r="G7" s="89">
         <f t="shared" si="0"/>
-        <v>0.39456612920912448</v>
+        <v>128191.68740968405</v>
       </c>
       <c r="H7" s="90">
         <f t="shared" si="1"/>
-        <v>3.3143554853566459E-2</v>
+        <v>10768.101742413461</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="23">
@@ -2277,11 +2270,11 @@
       </c>
       <c r="L7" s="9">
         <f t="shared" si="2"/>
-        <v>128191.68740968405</v>
+        <v>267151.04885209748</v>
       </c>
       <c r="M7" s="96">
         <f t="shared" si="3"/>
-        <v>133319.35490607141</v>
+        <v>277837.09080618137</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2296,14 +2289,15 @@
       </c>
       <c r="D8" s="52"/>
       <c r="E8" s="23">
-        <v>86881.922399999981</v>
+        <v>124715.18209999996</v>
       </c>
       <c r="F8" s="46">
-        <v>90358</v>
+        <f>E8</f>
+        <v>124715.18209999996</v>
       </c>
       <c r="G8" s="89">
         <f t="shared" si="0"/>
-        <v>-3476.0776000000187</v>
+        <v>0</v>
       </c>
       <c r="H8" s="90">
         <f t="shared" si="1"/>
@@ -2319,11 +2313,11 @@
       </c>
       <c r="L8" s="9">
         <f t="shared" si="2"/>
-        <v>124715.18209999996</v>
+        <v>128191.25969999998</v>
       </c>
       <c r="M8" s="96">
         <f t="shared" si="3"/>
-        <v>129703.78938399996</v>
+        <v>133318.91008799998</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2338,11 +2332,11 @@
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="23">
-        <v>90357</v>
+        <v>133319</v>
       </c>
       <c r="F9" s="46">
         <f>E9</f>
-        <v>90357</v>
+        <v>133319</v>
       </c>
       <c r="G9" s="89">
         <f t="shared" si="0"/>
@@ -2384,19 +2378,19 @@
       </c>
       <c r="E10" s="101">
         <f>SUM(E5:E9)</f>
-        <v>626512.0681541292</v>
+        <v>615965.88039768394</v>
       </c>
       <c r="F10" s="101">
         <f>SUM(F5:F9)</f>
-        <v>630015</v>
+        <v>484610.18209999998</v>
       </c>
       <c r="G10" s="101">
         <f t="shared" si="4"/>
-        <v>-27.248812000034377</v>
+        <v>3164.0108879999461</v>
       </c>
       <c r="H10" s="101">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>265.77691459199548</v>
       </c>
       <c r="I10" s="102">
         <f t="shared" si="4"/>
@@ -2412,56 +2406,56 @@
       </c>
       <c r="L10" s="101">
         <f>SUM(L5:L9)</f>
-        <v>606931.67129768396</v>
+        <v>752824.14695468929</v>
       </c>
       <c r="M10" s="104">
         <f>SUM(M5:M9)</f>
-        <v>631208.93814959121</v>
+        <v>782937.11283287697</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="122"/>
+      <c r="A11" s="131"/>
+      <c r="B11" s="131"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="131"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="123" t="s">
+      <c r="C14" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="124"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="119"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="116"/>
       <c r="J14" s="59"/>
       <c r="K14" s="60"/>
       <c r="L14" s="64"/>
     </row>
     <row r="15" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="125" t="s">
+      <c r="C15" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="124"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="124"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="124"/>
-      <c r="I15" s="119"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="116"/>
       <c r="J15" s="61"/>
       <c r="K15" s="62"/>
       <c r="L15" s="64"/>
@@ -2533,15 +2527,15 @@
       </c>
     </row>
     <row r="19" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C19" s="126" t="s">
+      <c r="C19" s="121" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="127"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="128"/>
+      <c r="D19" s="122"/>
+      <c r="E19" s="122"/>
+      <c r="F19" s="122"/>
+      <c r="G19" s="122"/>
+      <c r="H19" s="122"/>
+      <c r="I19" s="123"/>
       <c r="J19" s="61"/>
       <c r="K19" s="62"/>
       <c r="L19" s="64"/>
@@ -2579,10 +2573,10 @@
       </c>
       <c r="H21" s="68"/>
       <c r="I21" s="62"/>
-      <c r="J21" s="129" t="s">
+      <c r="J21" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="K21" s="130"/>
+      <c r="K21" s="112"/>
       <c r="L21" s="78"/>
     </row>
     <row r="22" spans="3:20" x14ac:dyDescent="0.25">
@@ -2612,8 +2606,8 @@
       <c r="G23" s="64"/>
       <c r="H23" s="64"/>
       <c r="I23" s="62"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="130"/>
+      <c r="J23" s="111"/>
+      <c r="K23" s="112"/>
       <c r="L23" s="78"/>
     </row>
     <row r="24" spans="3:20" x14ac:dyDescent="0.25">
@@ -2742,47 +2736,47 @@
       <c r="L31" s="64"/>
     </row>
     <row r="32" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="116" t="s">
+      <c r="C32" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="118">
+      <c r="D32" s="114"/>
+      <c r="E32" s="114"/>
+      <c r="F32" s="114"/>
+      <c r="G32" s="114"/>
+      <c r="H32" s="115">
         <f>SUM(H24:H31)</f>
         <v>167453.2965</v>
       </c>
-      <c r="I32" s="119"/>
+      <c r="I32" s="116"/>
       <c r="J32" s="72"/>
       <c r="K32" s="73"/>
       <c r="L32" s="64"/>
     </row>
     <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="123" t="s">
+      <c r="C36" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="119"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="119"/>
+      <c r="G36" s="119"/>
+      <c r="H36" s="119"/>
+      <c r="I36" s="116"/>
       <c r="J36" s="59"/>
       <c r="K36" s="60"/>
       <c r="L36" s="64"/>
     </row>
     <row r="37" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="125" t="s">
+      <c r="C37" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="124"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="124"/>
-      <c r="G37" s="124"/>
-      <c r="H37" s="124"/>
-      <c r="I37" s="119"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="119"/>
+      <c r="G37" s="119"/>
+      <c r="H37" s="119"/>
+      <c r="I37" s="116"/>
       <c r="J37" s="61"/>
       <c r="K37" s="62"/>
       <c r="L37" s="64"/>
@@ -2831,15 +2825,15 @@
       <c r="L40" s="64"/>
     </row>
     <row r="41" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C41" s="126" t="s">
+      <c r="C41" s="121" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="127"/>
-      <c r="E41" s="127"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="128"/>
+      <c r="D41" s="122"/>
+      <c r="E41" s="122"/>
+      <c r="F41" s="122"/>
+      <c r="G41" s="122"/>
+      <c r="H41" s="122"/>
+      <c r="I41" s="123"/>
       <c r="J41" s="61"/>
       <c r="K41" s="62"/>
       <c r="L41" s="64"/>
@@ -2871,10 +2865,10 @@
       </c>
       <c r="H43" s="68"/>
       <c r="I43" s="62"/>
-      <c r="J43" s="129" t="s">
+      <c r="J43" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="K43" s="130"/>
+      <c r="K43" s="112"/>
       <c r="L43" s="78"/>
     </row>
     <row r="44" spans="3:12" x14ac:dyDescent="0.25">
@@ -2904,8 +2898,8 @@
       <c r="G45" s="64"/>
       <c r="H45" s="64"/>
       <c r="I45" s="62"/>
-      <c r="J45" s="131"/>
-      <c r="K45" s="130"/>
+      <c r="J45" s="111"/>
+      <c r="K45" s="112"/>
       <c r="L45" s="78"/>
     </row>
     <row r="46" spans="3:12" x14ac:dyDescent="0.25">
@@ -2950,47 +2944,47 @@
       <c r="L48" s="64"/>
     </row>
     <row r="49" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="116" t="s">
+      <c r="C49" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="117"/>
-      <c r="E49" s="117"/>
-      <c r="F49" s="117"/>
-      <c r="G49" s="117"/>
-      <c r="H49" s="118">
+      <c r="D49" s="114"/>
+      <c r="E49" s="114"/>
+      <c r="F49" s="114"/>
+      <c r="G49" s="114"/>
+      <c r="H49" s="115">
         <f>M6</f>
         <v>101576.312448</v>
       </c>
-      <c r="I49" s="119"/>
+      <c r="I49" s="116"/>
       <c r="J49" s="72"/>
       <c r="K49" s="73"/>
       <c r="L49" s="64"/>
     </row>
     <row r="51" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="52" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="123" t="s">
+      <c r="C52" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="124"/>
-      <c r="E52" s="124"/>
-      <c r="F52" s="124"/>
-      <c r="G52" s="124"/>
-      <c r="H52" s="124"/>
-      <c r="I52" s="119"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="119"/>
+      <c r="F52" s="119"/>
+      <c r="G52" s="119"/>
+      <c r="H52" s="119"/>
+      <c r="I52" s="116"/>
       <c r="J52" s="59"/>
       <c r="K52" s="60"/>
       <c r="L52" s="64"/>
     </row>
     <row r="53" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="125" t="s">
+      <c r="C53" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="D53" s="124"/>
-      <c r="E53" s="124"/>
-      <c r="F53" s="124"/>
-      <c r="G53" s="124"/>
-      <c r="H53" s="124"/>
-      <c r="I53" s="119"/>
+      <c r="D53" s="119"/>
+      <c r="E53" s="119"/>
+      <c r="F53" s="119"/>
+      <c r="G53" s="119"/>
+      <c r="H53" s="119"/>
+      <c r="I53" s="116"/>
       <c r="J53" s="61"/>
       <c r="K53" s="62"/>
       <c r="L53" s="64"/>
@@ -3039,15 +3033,15 @@
       <c r="L56" s="64"/>
     </row>
     <row r="57" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C57" s="126" t="s">
+      <c r="C57" s="121" t="s">
         <v>49</v>
       </c>
-      <c r="D57" s="127"/>
-      <c r="E57" s="127"/>
-      <c r="F57" s="127"/>
-      <c r="G57" s="127"/>
-      <c r="H57" s="127"/>
-      <c r="I57" s="128"/>
+      <c r="D57" s="122"/>
+      <c r="E57" s="122"/>
+      <c r="F57" s="122"/>
+      <c r="G57" s="122"/>
+      <c r="H57" s="122"/>
+      <c r="I57" s="123"/>
       <c r="J57" s="61"/>
       <c r="K57" s="62"/>
       <c r="L57" s="64"/>
@@ -3079,10 +3073,10 @@
       </c>
       <c r="H59" s="68"/>
       <c r="I59" s="62"/>
-      <c r="J59" s="129" t="s">
+      <c r="J59" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="K59" s="130"/>
+      <c r="K59" s="112"/>
       <c r="L59" s="78"/>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.25">
@@ -3112,8 +3106,8 @@
       <c r="G61" s="64"/>
       <c r="H61" s="64"/>
       <c r="I61" s="62"/>
-      <c r="J61" s="131"/>
-      <c r="K61" s="130"/>
+      <c r="J61" s="111"/>
+      <c r="K61" s="112"/>
       <c r="L61" s="78"/>
     </row>
     <row r="62" spans="3:12" x14ac:dyDescent="0.25">
@@ -3266,47 +3260,47 @@
       <c r="L71" s="64"/>
     </row>
     <row r="72" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="116" t="s">
+      <c r="C72" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D72" s="117"/>
-      <c r="E72" s="117"/>
-      <c r="F72" s="117"/>
-      <c r="G72" s="117"/>
-      <c r="H72" s="118">
+      <c r="D72" s="114"/>
+      <c r="E72" s="114"/>
+      <c r="F72" s="114"/>
+      <c r="G72" s="114"/>
+      <c r="H72" s="115">
         <f>SUM(H62:H71)</f>
         <v>167453.2965</v>
       </c>
-      <c r="I72" s="119"/>
+      <c r="I72" s="116"/>
       <c r="J72" s="72"/>
       <c r="K72" s="73"/>
       <c r="L72" s="64"/>
     </row>
     <row r="75" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="123" t="s">
+      <c r="C76" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="124"/>
-      <c r="E76" s="124"/>
-      <c r="F76" s="124"/>
-      <c r="G76" s="124"/>
-      <c r="H76" s="124"/>
-      <c r="I76" s="119"/>
+      <c r="D76" s="119"/>
+      <c r="E76" s="119"/>
+      <c r="F76" s="119"/>
+      <c r="G76" s="119"/>
+      <c r="H76" s="119"/>
+      <c r="I76" s="116"/>
       <c r="J76" s="59"/>
       <c r="K76" s="60"/>
       <c r="L76" s="64"/>
     </row>
     <row r="77" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="125" t="s">
+      <c r="C77" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="D77" s="124"/>
-      <c r="E77" s="124"/>
-      <c r="F77" s="124"/>
-      <c r="G77" s="124"/>
-      <c r="H77" s="124"/>
-      <c r="I77" s="119"/>
+      <c r="D77" s="119"/>
+      <c r="E77" s="119"/>
+      <c r="F77" s="119"/>
+      <c r="G77" s="119"/>
+      <c r="H77" s="119"/>
+      <c r="I77" s="116"/>
       <c r="J77" s="61"/>
       <c r="K77" s="62"/>
       <c r="L77" s="64"/>
@@ -3355,15 +3349,15 @@
       <c r="L80" s="64"/>
     </row>
     <row r="81" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C81" s="126" t="s">
+      <c r="C81" s="121" t="s">
         <v>49</v>
       </c>
-      <c r="D81" s="127"/>
-      <c r="E81" s="127"/>
-      <c r="F81" s="127"/>
-      <c r="G81" s="127"/>
-      <c r="H81" s="127"/>
-      <c r="I81" s="128"/>
+      <c r="D81" s="122"/>
+      <c r="E81" s="122"/>
+      <c r="F81" s="122"/>
+      <c r="G81" s="122"/>
+      <c r="H81" s="122"/>
+      <c r="I81" s="123"/>
       <c r="J81" s="61"/>
       <c r="K81" s="62"/>
       <c r="L81" s="64"/>
@@ -3395,10 +3389,10 @@
       </c>
       <c r="H83" s="68"/>
       <c r="I83" s="62"/>
-      <c r="J83" s="129" t="s">
+      <c r="J83" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="K83" s="130"/>
+      <c r="K83" s="112"/>
       <c r="L83" s="78"/>
     </row>
     <row r="84" spans="3:12" x14ac:dyDescent="0.25">
@@ -3428,8 +3422,8 @@
       <c r="G85" s="64"/>
       <c r="H85" s="64"/>
       <c r="I85" s="62"/>
-      <c r="J85" s="131"/>
-      <c r="K85" s="130"/>
+      <c r="J85" s="111"/>
+      <c r="K85" s="112"/>
       <c r="L85" s="78"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.25">
@@ -3557,47 +3551,47 @@
       <c r="L93" s="64"/>
     </row>
     <row r="94" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="116" t="s">
+      <c r="C94" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D94" s="117"/>
-      <c r="E94" s="117"/>
-      <c r="F94" s="117"/>
-      <c r="G94" s="117"/>
-      <c r="H94" s="118">
+      <c r="D94" s="114"/>
+      <c r="E94" s="114"/>
+      <c r="F94" s="114"/>
+      <c r="G94" s="114"/>
+      <c r="H94" s="115">
         <f>SUM(H86:H93)</f>
         <v>167453.2965</v>
       </c>
-      <c r="I94" s="119"/>
+      <c r="I94" s="116"/>
       <c r="J94" s="72"/>
       <c r="K94" s="73"/>
       <c r="L94" s="64"/>
     </row>
     <row r="97" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="98" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="123" t="s">
+      <c r="C98" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="D98" s="124"/>
-      <c r="E98" s="124"/>
-      <c r="F98" s="124"/>
-      <c r="G98" s="124"/>
-      <c r="H98" s="124"/>
-      <c r="I98" s="119"/>
+      <c r="D98" s="119"/>
+      <c r="E98" s="119"/>
+      <c r="F98" s="119"/>
+      <c r="G98" s="119"/>
+      <c r="H98" s="119"/>
+      <c r="I98" s="116"/>
       <c r="J98" s="59"/>
       <c r="K98" s="60"/>
       <c r="L98" s="64"/>
     </row>
     <row r="99" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="125" t="s">
+      <c r="C99" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="D99" s="124"/>
-      <c r="E99" s="124"/>
-      <c r="F99" s="124"/>
-      <c r="G99" s="124"/>
-      <c r="H99" s="124"/>
-      <c r="I99" s="119"/>
+      <c r="D99" s="119"/>
+      <c r="E99" s="119"/>
+      <c r="F99" s="119"/>
+      <c r="G99" s="119"/>
+      <c r="H99" s="119"/>
+      <c r="I99" s="116"/>
       <c r="J99" s="61"/>
       <c r="K99" s="62"/>
       <c r="L99" s="64"/>
@@ -3646,15 +3640,15 @@
       <c r="L102" s="64"/>
     </row>
     <row r="103" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C103" s="126" t="s">
+      <c r="C103" s="121" t="s">
         <v>49</v>
       </c>
-      <c r="D103" s="127"/>
-      <c r="E103" s="127"/>
-      <c r="F103" s="127"/>
-      <c r="G103" s="127"/>
-      <c r="H103" s="127"/>
-      <c r="I103" s="128"/>
+      <c r="D103" s="122"/>
+      <c r="E103" s="122"/>
+      <c r="F103" s="122"/>
+      <c r="G103" s="122"/>
+      <c r="H103" s="122"/>
+      <c r="I103" s="123"/>
       <c r="J103" s="61"/>
       <c r="K103" s="62"/>
       <c r="L103" s="64"/>
@@ -3686,10 +3680,10 @@
       </c>
       <c r="H105" s="68"/>
       <c r="I105" s="62"/>
-      <c r="J105" s="129" t="s">
+      <c r="J105" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="K105" s="130"/>
+      <c r="K105" s="112"/>
       <c r="L105" s="78"/>
     </row>
     <row r="106" spans="3:12" x14ac:dyDescent="0.25">
@@ -3718,8 +3712,8 @@
       <c r="G107" s="64"/>
       <c r="H107" s="64"/>
       <c r="I107" s="62"/>
-      <c r="J107" s="131"/>
-      <c r="K107" s="130"/>
+      <c r="J107" s="111"/>
+      <c r="K107" s="112"/>
       <c r="L107" s="78"/>
     </row>
     <row r="108" spans="3:12" x14ac:dyDescent="0.25">
@@ -3847,47 +3841,24 @@
       <c r="L115" s="64"/>
     </row>
     <row r="116" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="116" t="s">
+      <c r="C116" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="D116" s="117"/>
-      <c r="E116" s="117"/>
-      <c r="F116" s="117"/>
-      <c r="G116" s="117"/>
-      <c r="H116" s="118">
+      <c r="D116" s="114"/>
+      <c r="E116" s="114"/>
+      <c r="F116" s="114"/>
+      <c r="G116" s="114"/>
+      <c r="H116" s="115">
         <f>SUM(H108:H115)</f>
         <v>167453.2965</v>
       </c>
-      <c r="I116" s="119"/>
+      <c r="I116" s="116"/>
       <c r="J116" s="72"/>
       <c r="K116" s="73"/>
       <c r="L116" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="J107:K107"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="C98:I98"/>
-    <mergeCell ref="C99:I99"/>
-    <mergeCell ref="C103:I103"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C77:I77"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="C52:I52"/>
-    <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C57:I57"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="C116:G116"/>
@@ -3904,6 +3875,29 @@
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C37:I37"/>
     <mergeCell ref="C41:I41"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="C98:I98"/>
+    <mergeCell ref="C99:I99"/>
+    <mergeCell ref="C103:I103"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H72:I72"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
